--- a/food_beverage_order_forms/031_salad_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/031_salad_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small_salad',_'label':_'small_salad'}</t>
+          <t>small_salad</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'small_salad', 'label': 'small_salad'}</t>
+          <t>small salad</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'large_salad',_'label':_'large_salad'}</t>
+          <t>large_salad</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'large_salad', 'label': 'large_salad'}</t>
+          <t>large salad</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'extra_large_salad',_'label':_'extra_large_salad'}</t>
+          <t>extra_large_salad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'extra_large_salad', 'label': 'extra_large_salad'}</t>
+          <t>extra large salad</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chicken',_'label':_'chicken'}</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chicken', 'label': 'chicken'}</t>
+          <t>chicken</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'steak',_'label':_'steak'}</t>
+          <t>steak</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'steak', 'label': 'steak'}</t>
+          <t>steak</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'salmon',_'label':_'salmon'}</t>
+          <t>salmon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'salmon', 'label': 'salmon'}</t>
+          <t>salmon</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'tofu',_'label':_'tofu'}</t>
+          <t>tofu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'tofu', 'label': 'tofu'}</t>
+          <t>tofu</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small',_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'small', 'label': 'small'}</t>
+          <t>small</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium', 'label': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large',_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'large', 'label': 'large'}</t>
+          <t>large</t>
         </is>
       </c>
     </row>
